--- a/r4-core-140-related-person/StructureDefinition-at-core-address.xlsx
+++ b/r4-core-140-related-person/StructureDefinition-at-core-address.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="240">
   <si>
     <t>Property</t>
   </si>
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-address</t>
+    <t>https://fhir.hl7.at/core/r4/StructureDefinition/at-core-address</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-07T11:53:41+00:00</t>
+    <t>2026-10-15T12:52:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -347,14 +347,30 @@
     <t>municipalityCode</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-ext-address-municipalityCode}
+    <t xml:space="preserve">Extension {https://fhir.hl7.at/core/r4/StructureDefinition/at-core-ext-address-municipalityCode}
 </t>
   </si>
   <si>
-    <t>Address Municipality Code</t>
-  </si>
-  <si>
-    <t>HL7® Austria FHIR® Core Extension for the municipality code part of the Austrian address</t>
+    <t>Address Municipality Code (Gemeindecode)</t>
+  </si>
+  <si>
+    <t>HL7® Austria FHIR® Core Extension for the municipality code (Gemeindecode) part of the Austrian address. The municipality code is related to the [municipality key (Gemeindekennziffer)](StructureDefinition-at-core-ext-address-municipalityKey.html). While these two are generally identical, there is one notable exception: in Vienna, the municipality key (Gemeindekennziffer) is consistently 90001, whereas the municipality code (Gemeindecode) varies by district. The current list of values is provided by [Statistik Austria](https://www.statistik.at/verzeichnis/reglisten/gemliste_knz.pdf).</t>
+  </si>
+  <si>
+    <t>Address.extension:municipalityKey</t>
+  </si>
+  <si>
+    <t>municipalityKey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://fhir.hl7.at/core/r4/StructureDefinition/at-core-ext-address-municipalityKey}
+</t>
+  </si>
+  <si>
+    <t>Address Municipality Key (Gemeindekennziffer)</t>
+  </si>
+  <si>
+    <t>HL7® Austria FHIR® Core Extension for the municipality key (Gemeindekennziffer) part of the Austrian address. The municipality key is related to the [municipality code (Gemeindecode)](StructureDefinition-at-core-ext-address-municipalityCode.html). While these two are generally identical, there is one notable exception: in Vienna, the municipality key (Gemeindekennziffer) is consistently 90001, whereas the municipality code (Gemeindecode) varies by district. The current list of values is provided by [Statistik Austria](https://www.statistik.at/verzeichnis/reglisten/gemliste_knz.pdf).</t>
   </si>
   <si>
     <t>Address.use</t>
@@ -557,7 +573,7 @@
     <t>additionalInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-ext-address-additionalInformation}
+    <t xml:space="preserve">Extension {https://fhir.hl7.at/core/r4/StructureDefinition/at-core-ext-address-additionalInformation}
 </t>
   </si>
   <si>
@@ -1050,7 +1066,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN22"/>
+  <dimension ref="A1:AN23"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="36.203125" customWidth="true" bestFit="true"/>
@@ -1063,7 +1079,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="92.1484375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="79.4921875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1675,9 +1691,11 @@
         <v>111</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="C6" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="C6" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="D6" t="s" s="2">
         <v>21</v>
       </c>
@@ -1692,10 +1710,10 @@
         <v>21</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="K6" t="s" s="2">
         <v>113</v>
@@ -1706,12 +1724,8 @@
       <c r="M6" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="N6" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="O6" t="s" s="2">
-        <v>117</v>
-      </c>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
         <v>21</v>
       </c>
@@ -1723,7 +1737,7 @@
         <v>21</v>
       </c>
       <c r="T6" t="s" s="2">
-        <v>118</v>
+        <v>21</v>
       </c>
       <c r="U6" t="s" s="2">
         <v>21</v>
@@ -1735,13 +1749,13 @@
         <v>21</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>119</v>
+        <v>21</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>120</v>
+        <v>21</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>121</v>
+        <v>21</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>21</v>
@@ -1759,28 +1773,28 @@
         <v>21</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>123</v>
+        <v>21</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>125</v>
+        <v>21</v>
       </c>
       <c r="AN6" t="s" s="2">
         <v>21</v>
@@ -1788,10 +1802,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1808,24 +1822,26 @@
         <v>21</v>
       </c>
       <c r="I7" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="O7" s="2"/>
+        <v>121</v>
+      </c>
+      <c r="O7" t="s" s="2">
+        <v>122</v>
+      </c>
       <c r="P7" t="s" s="2">
         <v>21</v>
       </c>
@@ -1837,7 +1853,7 @@
         <v>21</v>
       </c>
       <c r="T7" t="s" s="2">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="U7" t="s" s="2">
         <v>21</v>
@@ -1849,13 +1865,13 @@
         <v>21</v>
       </c>
       <c r="X7" t="s" s="2">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="Y7" t="s" s="2">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="Z7" t="s" s="2">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="AA7" t="s" s="2">
         <v>21</v>
@@ -1873,7 +1889,7 @@
         <v>21</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
@@ -1885,27 +1901,27 @@
         <v>21</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>134</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1925,23 +1941,21 @@
         <v>21</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O8" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
         <v>21</v>
       </c>
@@ -1953,7 +1967,7 @@
         <v>21</v>
       </c>
       <c r="T8" t="s" s="2">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="U8" t="s" s="2">
         <v>21</v>
@@ -1965,13 +1979,13 @@
         <v>21</v>
       </c>
       <c r="X8" t="s" s="2">
-        <v>21</v>
+        <v>124</v>
       </c>
       <c r="Y8" t="s" s="2">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="Z8" t="s" s="2">
-        <v>21</v>
+        <v>137</v>
       </c>
       <c r="AA8" t="s" s="2">
         <v>21</v>
@@ -1989,7 +2003,7 @@
         <v>21</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -2001,27 +2015,27 @@
         <v>21</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2032,7 +2046,7 @@
         <v>78</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>21</v>
@@ -2041,19 +2055,23 @@
         <v>21</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="K9" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
+        <v>142</v>
+      </c>
+      <c r="N9" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O9" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="P9" t="s" s="2">
         <v>21</v>
       </c>
@@ -2065,75 +2083,75 @@
         <v>21</v>
       </c>
       <c r="T9" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="U9" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V9" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W9" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X9" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y9" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z9" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA9" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB9" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD9" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF9" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AG9" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH9" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI9" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ9" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="AK9" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="AL9" t="s" s="2">
         <v>147</v>
       </c>
-      <c r="U9" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V9" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W9" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X9" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y9" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z9" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA9" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB9" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD9" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE9" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF9" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="AG9" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH9" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI9" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ9" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AK9" t="s" s="2">
+      <c r="AM9" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN9" t="s" s="2">
         <v>148</v>
-      </c>
-      <c r="AL9" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="AM9" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="AN9" t="s" s="2">
-        <v>151</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2144,7 +2162,7 @@
         <v>78</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>21</v>
@@ -2153,16 +2171,16 @@
         <v>21</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="K10" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2177,7 +2195,7 @@
         <v>21</v>
       </c>
       <c r="T10" t="s" s="2">
-        <v>21</v>
+        <v>152</v>
       </c>
       <c r="U10" t="s" s="2">
         <v>21</v>
@@ -2213,39 +2231,39 @@
         <v>21</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>93</v>
+        <v>149</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>21</v>
+        <v>127</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>21</v>
+        <v>153</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>21</v>
+        <v>154</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>21</v>
+        <v>155</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2256,7 +2274,7 @@
         <v>78</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>21</v>
@@ -2268,13 +2286,13 @@
         <v>21</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2313,29 +2331,31 @@
         <v>21</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AC11" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC11" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD11" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>21</v>
@@ -2352,14 +2372,12 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="C12" t="s" s="2">
-        <v>151</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
         <v>21</v>
       </c>
@@ -2368,7 +2386,7 @@
         <v>78</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>21</v>
@@ -2380,13 +2398,13 @@
         <v>21</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>159</v>
+        <v>97</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2425,16 +2443,14 @@
         <v>21</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="AC12" s="2"/>
       <c r="AD12" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="AF12" t="s" s="2">
         <v>104</v>
@@ -2455,7 +2471,7 @@
         <v>21</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>162</v>
+        <v>21</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>21</v>
@@ -2469,10 +2485,10 @@
         <v>163</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>21</v>
@@ -2494,13 +2510,13 @@
         <v>21</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2560,7 +2576,7 @@
         <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>105</v>
@@ -2569,7 +2585,7 @@
         <v>21</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>21</v>
@@ -2580,13 +2596,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="C14" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="C14" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="D14" t="s" s="2">
         <v>21</v>
@@ -2608,10 +2624,10 @@
         <v>21</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="L14" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="L14" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="M14" t="s" s="2">
         <v>172</v>
@@ -2674,7 +2690,7 @@
         <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>105</v>
@@ -2697,7 +2713,7 @@
         <v>174</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C15" t="s" s="2">
         <v>175</v>
@@ -2728,7 +2744,7 @@
         <v>177</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2797,7 +2813,7 @@
         <v>21</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>21</v>
+        <v>178</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>21</v>
@@ -2811,9 +2827,11 @@
         <v>179</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="C16" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>180</v>
+      </c>
       <c r="D16" t="s" s="2">
         <v>21</v>
       </c>
@@ -2834,13 +2852,13 @@
         <v>21</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>90</v>
+        <v>181</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2864,7 +2882,7 @@
         <v>21</v>
       </c>
       <c r="W16" t="s" s="2">
-        <v>182</v>
+        <v>21</v>
       </c>
       <c r="X16" t="s" s="2">
         <v>21</v>
@@ -2891,19 +2909,19 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>183</v>
+        <v>104</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>21</v>
@@ -2927,7 +2945,7 @@
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>185</v>
+        <v>21</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -2943,16 +2961,16 @@
         <v>21</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="K17" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2967,43 +2985,43 @@
         <v>21</v>
       </c>
       <c r="T17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="X17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="U17" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V17" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W17" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X17" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z17" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>184</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3015,38 +3033,38 @@
         <v>21</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>122</v>
+        <v>21</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>189</v>
+        <v>21</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>190</v>
+        <v>21</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>192</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>21</v>
@@ -3055,20 +3073,18 @@
         <v>21</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="K18" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>21</v>
@@ -3081,7 +3097,7 @@
         <v>21</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="U18" t="s" s="2">
         <v>21</v>
@@ -3117,7 +3133,7 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3129,38 +3145,38 @@
         <v>21</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>21</v>
+        <v>196</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>21</v>
+        <v>197</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>21</v>
@@ -3169,18 +3185,20 @@
         <v>21</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="K19" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>202</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>21</v>
@@ -3193,7 +3211,7 @@
         <v>21</v>
       </c>
       <c r="T19" t="s" s="2">
-        <v>21</v>
+        <v>203</v>
       </c>
       <c r="U19" t="s" s="2">
         <v>21</v>
@@ -3229,7 +3247,7 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3241,31 +3259,31 @@
         <v>21</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AL19" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="AL19" t="s" s="2">
-        <v>206</v>
-      </c>
       <c r="AM19" t="s" s="2">
-        <v>207</v>
+        <v>21</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>208</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3281,16 +3299,16 @@
         <v>21</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="K20" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3305,7 +3323,7 @@
         <v>21</v>
       </c>
       <c r="T20" t="s" s="2">
-        <v>213</v>
+        <v>21</v>
       </c>
       <c r="U20" t="s" s="2">
         <v>21</v>
@@ -3341,7 +3359,7 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3353,31 +3371,31 @@
         <v>21</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>21</v>
+        <v>215</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3393,20 +3411,18 @@
         <v>21</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="K21" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>221</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>21</v>
@@ -3419,7 +3435,7 @@
         <v>21</v>
       </c>
       <c r="T21" t="s" s="2">
-        <v>21</v>
+        <v>218</v>
       </c>
       <c r="U21" t="s" s="2">
         <v>21</v>
@@ -3455,7 +3471,7 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3467,27 +3483,27 @@
         <v>21</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="AN21" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="AL21" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>225</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3498,7 +3514,7 @@
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>21</v>
@@ -3507,21 +3523,21 @@
         <v>21</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>227</v>
+        <v>90</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N22" s="2"/>
-      <c r="O22" t="s" s="2">
-        <v>230</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>21</v>
       </c>
@@ -3533,7 +3549,7 @@
         <v>21</v>
       </c>
       <c r="T22" t="s" s="2">
-        <v>231</v>
+        <v>21</v>
       </c>
       <c r="U22" t="s" s="2">
         <v>21</v>
@@ -3569,7 +3585,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -3581,18 +3597,132 @@
         <v>21</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AN22" t="s" s="2">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E23" s="2"/>
+      <c r="F23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J23" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="K23" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="AL22" t="s" s="2">
+      <c r="L23" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="AM22" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="AN22" t="s" s="2">
+      <c r="N23" s="2"/>
+      <c r="O23" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="P23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q23" s="2"/>
+      <c r="R23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T23" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="U23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF23" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH23" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="AK23" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AN23" t="s" s="2">
         <v>21</v>
       </c>
     </row>
